--- a/sample_data/00_材料清单与说明/材料提交清单.xlsx
+++ b/sample_data/00_材料清单与说明/材料提交清单.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,7 +464,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>铁路工程投标模板_通用版.docx</t>
+          <t>铁路工程投标模板1-工程化.docx</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -484,7 +484,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>含占位符</t>
+          <t>电气火灾监控类</t>
         </is>
       </c>
     </row>
@@ -494,17 +494,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>03_历史投标文件/完整历史标书/</t>
+          <t>02_Word标书模板/标准投标Word模板/</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>历史标书_京沪高铁XX段_2024.docx</t>
+          <t>铁路工程投标模板3-工程化.docx</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>历史标书</t>
+          <t>Word模板</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>RTU及能管系统类</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,17 +529,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>04_结构化字段与录入规范/</t>
+          <t>03_历史投标文件/完整历史标书/</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>标书关键字段清单.xlsx</t>
+          <t>历史标书-地铁12号线电气火灾监控-2025.docx</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>字段清单</t>
+          <t>历史标书</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -552,21 +556,21 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>05_条目完整性校验清单/</t>
+          <t>04_结构化字段与录入规范/</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>商务标条目清单.xlsx</t>
+          <t>标书关键字段清单.xlsx</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>条目清单</t>
+          <t>字段清单</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -583,21 +587,21 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>06_资质数据库参考材料/</t>
+          <t>05_条目完整性校验清单/</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>资质材料清单.xlsx</t>
+          <t>商务标条目清单.xlsx</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>资质清单</t>
+          <t>条目清单</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -614,34 +618,65 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>06_资质数据库参考材料/</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>资质材料清单.xlsx</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>资质清单</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>必填</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>07_企业问答Chatbot参考/</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>招标常见问题与标准答案.xlsx</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>必填</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
